--- a/diseases/d108/1995-1999.xlsx
+++ b/diseases/d108/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>3</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>7</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>5</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>9</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>4</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>8</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>3</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10590,9 +10515,6 @@
       <c r="O52" t="n">
         <v>2</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10983,9 +10905,6 @@
       <c r="O54" t="n">
         <v>3</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="S54" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11376,9 +11295,6 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11769,9 +11685,6 @@
       <c r="O58" t="n">
         <v>5</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12162,9 +12075,6 @@
       <c r="O60" t="n">
         <v>2</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12555,9 +12465,6 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12948,9 +12855,6 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13341,9 +13245,6 @@
       <c r="O66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13734,9 +13635,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14127,9 +14025,6 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14520,9 +14415,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14913,9 +14805,6 @@
       <c r="O74" t="n">
         <v>6</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15306,9 +15195,6 @@
       <c r="O76" t="n">
         <v>3</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15699,9 +15585,6 @@
       <c r="O78" t="n">
         <v>7</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16092,9 +15975,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16485,9 +16365,6 @@
       <c r="O82" t="n">
         <v>7</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16878,9 +16755,6 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17271,9 +17145,6 @@
       <c r="O86" t="n">
         <v>6</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17664,9 +17535,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18057,9 +17925,6 @@
       <c r="O90" t="n">
         <v>4</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18450,9 +18315,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18843,9 +18705,6 @@
       <c r="O94" t="n">
         <v>4</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19236,9 +19095,6 @@
       <c r="O96" t="n">
         <v>2</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19629,9 +19485,6 @@
       <c r="O98" t="n">
         <v>4</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20022,9 +19875,6 @@
       <c r="O100" t="n">
         <v>2</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20415,9 +20265,6 @@
       <c r="O102" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20808,9 +20655,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21201,9 +21045,6 @@
       <c r="O106" t="n">
         <v>2</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21594,9 +21435,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="S108" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21987,9 +21825,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22380,9 +22215,6 @@
       <c r="O112" t="n">
         <v>2</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="S112" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22773,9 +22605,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23166,9 +22995,6 @@
       <c r="O116" t="n">
         <v>2</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23559,9 +23385,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23952,9 +23775,6 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24345,9 +24165,6 @@
       <c r="O122" t="n">
         <v>3</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24738,9 +24555,6 @@
       <c r="O124" t="n">
         <v>12</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25131,9 +24945,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25524,9 +25335,6 @@
       <c r="O128" t="n">
         <v>4</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25917,9 +25725,6 @@
       <c r="O130" t="n">
         <v>2</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26310,9 +26115,6 @@
       <c r="O132" t="n">
         <v>19</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26703,9 +26505,6 @@
       <c r="O134" t="n">
         <v>3</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27096,9 +26895,6 @@
       <c r="O136" t="n">
         <v>15</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27489,9 +27285,6 @@
       <c r="O138" t="n">
         <v>3</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27882,9 +27675,6 @@
       <c r="O140" t="n">
         <v>12</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28275,9 +28065,6 @@
       <c r="O142" t="n">
         <v>2</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28668,9 +28455,6 @@
       <c r="O144" t="n">
         <v>19</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29061,9 +28845,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29454,9 +29235,6 @@
       <c r="O148" t="n">
         <v>13</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="S148" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29847,9 +29625,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30240,9 +30015,6 @@
       <c r="O152" t="n">
         <v>4</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30633,9 +30405,6 @@
       <c r="O154" t="n">
         <v>2</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31026,9 +30795,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31419,9 +31185,6 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31812,9 +31575,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32205,9 +31965,6 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="S162" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32598,9 +32355,6 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32991,9 +32745,6 @@
       <c r="O166" t="n">
         <v>1</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33384,9 +33135,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33777,9 +33525,6 @@
       <c r="O170" t="n">
         <v>4</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34170,9 +33915,6 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34563,9 +34305,6 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="S174" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34956,9 +34695,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35349,9 +35085,6 @@
       <c r="O178" t="n">
         <v>4</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35742,9 +35475,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36135,9 +35865,6 @@
       <c r="O182" t="n">
         <v>2</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36528,9 +36255,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36921,9 +36645,6 @@
       <c r="O186" t="n">
         <v>8</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37314,9 +37035,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37707,9 +37425,6 @@
       <c r="O190" t="n">
         <v>3</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="S190" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38100,9 +37815,6 @@
       <c r="O192" t="n">
         <v>2</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38493,9 +38205,6 @@
       <c r="O194" t="n">
         <v>6</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="S194" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38886,9 +38595,6 @@
       <c r="O196" t="n">
         <v>2</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="S196" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39279,9 +38985,6 @@
       <c r="O198" t="n">
         <v>10</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -39672,9 +39375,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40065,9 +39765,6 @@
       <c r="O202" t="n">
         <v>1</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="S202" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40458,9 +40155,6 @@
       <c r="O204" t="n">
         <v>3</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -40851,9 +40545,6 @@
       <c r="O206" t="n">
         <v>1</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41244,9 +40935,6 @@
       <c r="O208" t="n">
         <v>8</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -41637,9 +41325,6 @@
       <c r="O210" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42030,9 +41715,6 @@
       <c r="O212" t="n">
         <v>2</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="S212" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42423,9 +42105,6 @@
       <c r="O214" t="n">
         <v>3</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -42816,9 +42495,6 @@
       <c r="O216" t="n">
         <v>1</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43209,9 +42885,6 @@
       <c r="O218" t="n">
         <v>1</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="S218" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43602,9 +43275,6 @@
       <c r="O220" t="n">
         <v>2</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -43995,9 +43665,6 @@
       <c r="O222" t="n">
         <v>1</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44388,9 +44055,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -44781,9 +44445,6 @@
       <c r="O226" t="n">
         <v>3</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45174,9 +44835,6 @@
       <c r="O228" t="n">
         <v>9</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45567,9 +45225,6 @@
       <c r="O230" t="n">
         <v>1</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -45960,9 +45615,6 @@
       <c r="O232" t="n">
         <v>3</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46353,9 +46005,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -46746,9 +46395,6 @@
       <c r="O236" t="n">
         <v>5</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="S236" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47139,9 +46785,6 @@
       <c r="O238" t="n">
         <v>2</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="S238" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47532,9 +47175,6 @@
       <c r="O240" t="n">
         <v>2</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -47925,9 +47565,6 @@
       <c r="O242" t="n">
         <v>1</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48318,9 +47955,6 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -48710,9 +48344,6 @@
       </c>
       <c r="O246" t="n">
         <v>4</v>
-      </c>
-      <c r="Q246" t="n">
-        <v>0</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
